--- a/StructureDefinition-Signatur.xlsx
+++ b/StructureDefinition-Signatur.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T08:41:45+00:00</t>
+    <t>2026-09-18T09:59:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-Signatur.xlsx
+++ b/StructureDefinition-Signatur.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T09:59:15+00:00</t>
+    <t>2026-09-18T10:29:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -78,7 +78,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Supporting logical model generated from gloo4.xmi (source class: Signatur).</t>
+    <t>Egenhändigt skriven namnteckning eller förkortad namnteckning.</t>
   </si>
   <si>
     <t>Purpose</t>
